--- a/src/attributions/attributions_ig_traj_89.xlsx
+++ b/src/attributions/attributions_ig_traj_89.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,52 +999,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.08002405806976164</v>
+        <v>0.09261250556947608</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.230202729308465</v>
+        <v>0.1062594343164217</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005108318808481852</v>
+        <v>-0.03824742361043373</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.03860066713380397</v>
+        <v>0.05047296759349478</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2075828185783251</v>
+        <v>-0.05355071755229394</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01204929019375068</v>
+        <v>-0.03296479912503028</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
         <v>-0</v>
@@ -1056,16 +1056,16 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.09806669489094141</v>
+        <v>0.01741185075773766</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01229636434604111</v>
+        <v>-0.097171563945867</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.004991894583601985</v>
+        <v>0.0571175129235493</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1077,109 +1077,109 @@
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03388509010844856</v>
+        <v>-0.004833637740037517</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.006056585975831554</v>
+        <v>-0.003621894068250127</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.004450682315163321</v>
+        <v>-0.01367343161788063</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.03033852235949213</v>
+        <v>0.1170350942805501</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.03456439921250479</v>
+        <v>-0.0142534923665989</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.06390532446227024</v>
+        <v>0.1799367582110867</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1606877030427201</v>
+        <v>0.264779241449016</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.07871500957670378</v>
+        <v>-0.04525111223060151</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.005945696286255524</v>
+        <v>0.01174238173842704</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01757312437285266</v>
+        <v>-0.05586103291185995</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.07897551879926892</v>
+        <v>0.08526019036090446</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.02712815448214431</v>
+        <v>-0.06695879410836027</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
         <v>-0</v>
@@ -1188,55 +1188,55 @@
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.03040979083744841</v>
+        <v>-0.0406585774400727</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.04594451529409452</v>
+        <v>-0.0697005414207504</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.08000625774407112</v>
+        <v>-0.01225505310310061</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.06713017421494699</v>
+        <v>0.1126391399033876</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.02182646807514023</v>
+        <v>-0.146035259425304</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.01884615699057904</v>
+        <v>-0.02453848340344639</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1245,49 +1245,49 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03283043049272813</v>
+        <v>-0.1323203861586752</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.03616967539422405</v>
+        <v>-0.04017157738314805</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01616340536772806</v>
+        <v>-0.01801573776434088</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.007863134234805585</v>
+        <v>-0.04257266995601617</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02819151524651156</v>
+        <v>0.1022671513078598</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.02816355631835672</v>
+        <v>0.02935888091787687</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
         <v>0</v>
@@ -1296,22 +1296,22 @@
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04648971561772923</v>
+        <v>-0.1333716340712582</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.04027009503825581</v>
+        <v>-0.03721409337048506</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01093820471416725</v>
+        <v>-0.008816641728710072</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1323,28 +1323,28 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.03395264743488322</v>
+        <v>-0.08211545964301138</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01468105289247713</v>
+        <v>0.06137740060148702</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.03297448683683691</v>
+        <v>-0.04081138523051327</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>-0</v>
@@ -1353,19 +1353,19 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.01918322500336656</v>
+        <v>-0.02346073295510074</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.04349730583284731</v>
+        <v>-0.06398017654509644</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.005621113725438998</v>
+        <v>0.04246628526769467</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1374,31 +1374,31 @@
         <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.06400284214897392</v>
+        <v>0.03320020543633161</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.0109657149773436</v>
+        <v>0.07530836824132721</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.02088623205835872</v>
+        <v>0.1816486346592184</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
@@ -1407,22 +1407,22 @@
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.03911788968558339</v>
+        <v>-0.1108103280948798</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.08937657361646349</v>
+        <v>0.1478624398499252</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.03570638022466691</v>
+        <v>0.01610882745589811</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1434,22 +1434,22 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.04835681117410522</v>
+        <v>-0.04413128947385306</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.0470410529826082</v>
+        <v>0.01342717299717842</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.01999236228472831</v>
+        <v>0.0004423023455411669</v>
       </c>
       <c r="ET2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
         <v>0</v>
@@ -1458,52 +1458,52 @@
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04098487980350489</v>
+        <v>-0.1688385000464569</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.03239473819547633</v>
+        <v>-0.009254652958006215</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01641101982812671</v>
+        <v>-0.00128894770166078</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.01242405373375696</v>
+        <v>-0.1658149906311707</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.00543148769200911</v>
+        <v>0.0469251726897654</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01687241999401279</v>
+        <v>0.0351278086727689</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
         <v>0</v>
@@ -1515,49 +1515,49 @@
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01297647463482977</v>
+        <v>-0.1566630247196962</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.006666584027607884</v>
+        <v>0.2564570279355521</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.008699428982887088</v>
+        <v>0.02461754634534308</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03139313018916433</v>
+        <v>-0.01575589222662263</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.01992368484076844</v>
+        <v>-0.04389835029754881</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,187 +1568,187 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.009766585838449441</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.006424466339783347</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.001758685965367484</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.008739215803511365</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>-0.001639284702146657</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.001952193455226982</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.02111110232566383</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.002360203805320813</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.009638903416346579</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.0009867130137587038</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.003630170488209579</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.003844242897738521</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.01154867834914742</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.01824623138038935</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-1.189604611930384e-05</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.003210038026790492</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.02154174475802197</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.006143544864556902</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.007171136466734018</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.01203470653240844</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.002018182318667575</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -1757,88 +1757,88 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.01052119768464915</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.001018972831787451</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.0003272250453652676</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.006810540386296638</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.01416650443050262</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.00731015370982669</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.005852311372872152</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.01262095476133505</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.002278459106587875</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0.00118434113258184</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,43 +1847,43 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.01258955186549956</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.005003838330725976</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.006065045207099116</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.01559080209137238</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.004063249873165298</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,52 +1892,52 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.001379130245323087</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.01213309333787943</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.001503962196789043</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.001153555554376322</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.01416908645705145</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.001430034865019307</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,64 +1946,64 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.009357864284606226</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY3" t="n">
         <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>-0.002827216076404153</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.0106529149994065</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.01252910976592873</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.01228331593948414</v>
       </c>
       <c r="EK3" t="n">
         <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.001367487136700384</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.001470742117387183</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
@@ -2012,22 +2012,22 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.008069597913782029</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.004008878226673914</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.007799043926247923</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
@@ -2036,55 +2036,55 @@
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.0172902394976263</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.006419501513918741</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.01638439146114723</v>
       </c>
       <c r="FH3" t="n">
         <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>-0.01058902312942136</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.002112838944926352</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0.009111541293323238</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,46 +2093,8581 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>0.003022008864256373</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0.008839221991827207</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.003728526205644093</v>
       </c>
       <c r="FZ3" t="n">
         <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.01419395558810409</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.2059509664588109</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07751039377416985</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1319313212495435</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.1604677325730401</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.09194819467272999</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.07877377525686328</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.06149463470715534</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.09569014014921989</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1068487071324895</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.0458253460015944</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.07357355580382799</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.01617053843441532</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.1824991964987688</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.1852939649609738</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.05209457012257063</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.5748004626080735</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.1125441018746224</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.1456723222017901</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.04272492430785278</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.03305559953331954</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.009093331458349495</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.0541059760840009</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-0.07630547010558554</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-0.06205269302203203</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.4156611595090754</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.07187203966595589</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.2033482093070215</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.2764158757677287</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.02265125427816255</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-0.1421797069807169</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.1806331997961204</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>-0.006595514811784739</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-0.07134206517453835</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.2769804344067274</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.03277900814224608</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>-0.1481387219190579</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.02075109581676206</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.02479735646509313</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>-0.0163383473539681</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.1650155689146413</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>-0.04297959813889379</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>-0.06292799997217616</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>-0.1384776363409609</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.0195727244102116</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.3264306565155873</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.181150030585191</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.02092613549490533</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>-0.07959287406116662</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.1542715563086323</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.0790436325609065</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.01397118417863401</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.2997366061663707</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.02351588045641247</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>-0.1385635530593989</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.1125666987988104</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.1006827612181083</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.02646531958093092</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.2811924933933202</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>-0.001202312287655217</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>-0.1826875607242791</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.13956609337206</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>-0.05223833902720283</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.00192290400866922</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.006270808877421302</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.00200543026864571</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.01381552820981235</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.03940600617521463</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.0007832848520710833</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.01263003060264237</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.01182495382148027</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.01838373121695332</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.024184130230594</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.003475642500536795</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.007089214085434164</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.0008138998678394694</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.0237758665084825</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.004951584453201198</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.02197051188685464</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.07762266619636328</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.002279791999151328</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.03420078760984031</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-0.03078300260432036</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.01425601811860896</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.02488158628603592</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.02468185919903191</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.01893886155547919</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0.001159769152235959</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.01292576214916349</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.01373841415697205</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.009743471211648775</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.009745798754902656</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.01586328331253902</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.007220841719477787</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.02186534821962742</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.03553405659875039</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.0120014808887587</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.01311971633242273</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.00728871816266481</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.005874529451389031</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0.005086873576324292</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.002255862200723793</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0.04684166303595946</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>-0.0193215156553774</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>-0.0007537063623008622</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0.02955101628993194</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>-0.0207380323479337</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>-0.02622320721026981</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0.01188256015774633</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0.001189444045793125</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0.00935028075798572</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0.01867915820041322</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>-0.03241339920147106</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>-0.01260176484242128</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0.006793954656442806</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>-0.01278296224539983</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0.01686617642127965</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>0.02003015295036237</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0.02148936497223416</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0.01055284828460342</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0.08632043324390505</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>-0.108314393065859</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0.003118645767450058</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>-0.00265471274343675</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>-0.003045953163110761</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.004545314794400178</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.07590371906918465</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.03726111994696193</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.01311603244663205</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06849974300540949</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.02232630677323928</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.01320191599771655</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.04140647745199336</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.003909859241501959</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.0006711658015362105</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.02010067701514188</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0324285580239525</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.03804143669790486</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.07167360744589046</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.03196774561600107</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.08438329361983492</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.1442151410896351</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.1186961246800363</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.003184128502808679</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.06650247160828848</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.07324753642242471</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.02664827936728288</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.0524372471400282</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.08375764734133714</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0.04965392679979439</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.1079447917355131</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.04577161101037096</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.03376637421739597</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>-0.01618108035920219</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.008532933217729251</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.004501816664978816</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.04115522288549514</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.08904984018136933</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.0287069212698262</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0.02216561557577012</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.01887823081273721</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.01642801303233913</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0.04392727761151576</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.004697808652314256</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0.0002961274016969365</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>-0.02148627405722929</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.03529661055588989</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0.03081318462721366</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0.04500506991941573</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.02767586125638432</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0.008856195916876227</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>-0.01690618184879141</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.02325102070322288</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0.01659331305838676</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>-0.05444659728980734</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.01845625712984147</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.03108296149794889</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>-0.02597138326668443</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.01389478533060132</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.05892733365741666</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0.0004624378975898934</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>-0.03067307176942984</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>-0.0004761598580145753</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.0009076567656679336</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0.01231833758076042</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.02757205330154083</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0.0798380351983817</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1220115557842236</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.0302921881480474</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.03697527225805009</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1557762117262881</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.06469888499266885</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.03344212221613328</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.07345849487106854</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.03509617395416281</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.03894154829087395</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.002940825305521666</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.01359797337829819</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.0253523283986961</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.01924570932961605</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.03249677382054659</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.03534663234685093</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.2820949926257814</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.1305533788626629</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.1176740364716378</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.04186734985312257</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0.0235008921677866</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.002728463570028218</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.09522757060192932</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.1053642222003507</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.06833264272892899</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.185108491788607</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0.05905573784105799</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-0.01366144047426692</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.04936834495137051</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.02977740897387005</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.02145370181246752</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0.05160890778846696</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.0424913672955718</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-0.0005742452871879848</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-0.04785552150298184</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0.0169320200652397</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0.02769620803762794</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0.037706293871182</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.01809299826608429</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0.004987237476563788</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0.00244872151721638</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0.03039236997475031</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>-0.01684611876728156</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0.04260790557847273</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>-0.1069415954339283</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0.0004376328231315452</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0.002449139430484887</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0.03258062283681647</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0.01612114703323796</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0.005538646464642032</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0.08118082006765139</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0.03378873682473866</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0.06014685418056922</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0.01173014322120235</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0.0139589751951285</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0.04047650313740387</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.06790066458638147</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>-0.008183255125926783</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0.0138754555332785</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0.02251435271529787</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>-0.07156702914652648</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>-0.04650450079728605</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0.02886784800641161</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2096693682134363</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.0750166166562424</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.002307426063447924</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2253538001784</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.09301972531986052</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.015131853562126</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.07253658711035076</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.049872696994281</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.05389043600810541</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.822321357005553e-11</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.03031412585523364</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.004850437478771981</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.08170577541812546</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.04832348710978294</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.06368426011152226</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.2492259918007632</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.07789402998217476</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.06586752572875919</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.01454259028151237</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.03161225769133517</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.0636501268802339</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.00833073295105412</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-0.01545823372011205</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.03820901211454331</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.1976160356112327</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.06554450728213003</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.03281088486024659</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.09433359455921464</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.07013279949674008</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0.01466912937720526</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.03942147540083039</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.08915625644284889</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.03178255810672126</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.08775673354521278</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.07537568967104406</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>-0.007571185944042888</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.05592850155723977</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.02099047027455515</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0.04721012094947515</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.04381214860849149</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0484020208394514</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.02383719647378245</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.06748996706205689</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>-0.03560130743106976</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.009379064723980585</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.05865114783757141</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.04827928976076753</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.003324001950410117</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.01721517515937239</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.02262920925917381</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.02530201705301468</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.1036778110082284</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.08291554424401187</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.02242927673519808</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.05820532839542775</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.06850991370386753</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0.02344542935721857</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.001699550966784807</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.0240667272872071</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>-0.01419298419946697</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.07576080848140845</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.01665392864350558</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2552942220753153</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.01023104018757836</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.04659350811553833</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.320796157533452</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.05980908884345715</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.02202421415641723</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.05796325890111347</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.05397997972710662</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.01588311784236237</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.002446248241939148</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-8.602804920814296e-11</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.007098523042614571</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.04326289551270661</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.0200412346151099</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.02853370114060446</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.3111072196327669</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.1565127624264403</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.04520026946744959</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.04693942047282854</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.03986508125838894</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0.06511005946714073</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.03521911949480092</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.05030005294287831</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-0.00772537827105485</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.2445101736078754</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.04567545861776077</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-0.028839889946557</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0.1014080672420287</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.004713823743566336</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.04459617233725707</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0.09735443377733193</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.05340361533077159</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.04887997385043591</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.1028741523381442</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.01223257853703146</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.03956234373569907</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.03643108596197547</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0.1164809551983115</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.02741135933776512</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0.06986055792893438</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.02147551992622085</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>-0.0304388039371654</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0.01022702842253267</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.04297421709793064</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>-0.08426571031217311</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0.0006421000903546931</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0.0514840122193429</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.01999988827872049</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0.01497817264687265</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.1126974921389493</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.06172705432639439</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0.1203447665895982</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0.01762598762817524</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.03618740535183632</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0.1514763835287932</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.1168245573813957</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.01413282509208374</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.002706839808738324</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.007023437467219743</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>-0.02185385862585302</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>-0.01118584998245237</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>-0.01411868844621811</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2572109199375562</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1398346330748678</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.03088504726051357</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2646325795175675</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.172478891787397</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.06492494406646997</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.06529898904722864</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.04993148936041014</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.05898996962726243</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.01304771955958171</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-6.816574537521338e-11</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.006474343085117038</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.08540464292294087</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.02320990833108592</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.05224757245832938</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.3030892495797154</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0.08577334330581109</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.1303509637467768</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.03225668879314386</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.06301959972660934</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-0.05405964290128979</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.01599505973801701</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.01821730399662032</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.04247560916093045</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.2190985757971085</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0.08464251971301259</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.05304923129423997</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-0.09724670430392422</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.07854249727123955</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0.004332206564096</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-0.04296277610018994</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.07402236436436549</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.04040323420071193</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-0.09633329650025615</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.08265730388036217</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.004891126253082832</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.05104871418035917</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.02230645585188406</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-0.07587327158594827</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>-0.06149316156660021</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.01315313454864719</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0.01803152969733429</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.07036138340538266</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.04718362474904518</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>-0.0142916802855103</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>-0.06413324297386513</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.07169848810348978</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.008556737037990409</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>-0.02290352825708888</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.07749679909375881</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0.03886115924946761</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>-0.1154491172373783</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.09436740994436894</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0.01096773474267319</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>-0.04995666505196271</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.06361841516033301</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.0126865396465982</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.0007876399790999658</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.1001700231626025</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.003179535762130721</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>-0.06414458562885869</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.03458413463532549</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4183901905802944</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1164827442632655</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.258506764453281</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.570974298614696</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.04147971025453896</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.2365913216506088</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.1554303993479813</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.1803210558146915</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.03286400820390464</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.02007933882809534</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.08375903108085359</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.0606200239177939</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1180608057081852</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.005972345172054185</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.237958846306118</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.8483570257339009</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.01300723935175771</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.214993493341022</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.155582185031378</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.2010416848984778</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.2256892191828704</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.1929843840707626</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.226929421007399</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-0.003265147687071619</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.4868393395516355</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.05515030202710412</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.2319944394041299</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.1961425274500776</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.03363894181371239</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.1082868116286367</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.236769780567819</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.1188482059392961</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.1661086743374795</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.19137038793728</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.04244395974832647</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.09925265099401941</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>-0.0604285371451871</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>-0.1310418190325006</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.06497920720839466</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.03093935080544544</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.08069811941796921</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.02532991561399286</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.1173595966831291</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>-0.005425291936226723</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.04191579586754969</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.0508150661317404</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.1238285390130989</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>-0.0453836347226242</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>-0.01713479602872287</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>-0.1069254068287484</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.1379577631556312</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.2132723900769284</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.06142476764519373</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.09994553088973782</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.2340194834777319</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.1691531238463859</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>-0.1758683120248455</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.04197726822775515</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.000998830484569402</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.07168195970983976</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.05244634028345758</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>-0.04791156687702534</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>-0.2087824726794484</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4076115825065665</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.01397992064360781</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.1904947379116486</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.5350114204244126</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.02806681663003321</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.05903286002179213</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.04474306474701543</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.268731350987188</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.02254465578766359</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.04468081697013588</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.1559429768874766</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.02976063973901485</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.1283945374077588</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.1956889207830254</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0.1706889414368647</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.3401723784861743</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.2962025541587214</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.09378270159535633</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.2187692603574305</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.2009247970196917</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-0.06018947369998107</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.1342379088130209</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.2897054389608547</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0.04076282889445466</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.199380385847901</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.1460065560610539</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.09872662512136116</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.1058657725320988</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.033932904594094</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0.01879218123018852</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.1448927200081195</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.01267460220146541</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.08261265872192268</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.1111128889591939</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.009068352809808451</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.05428205093285363</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.01881287878307421</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.09381580550504502</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.05089864263863798</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-0.2137523970526683</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>-0.03708151513301718</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0.08251251224379924</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0.2259525794813951</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>-0.1427706790810501</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.07476480265862261</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.02423553696093864</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.05141302952308439</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.04743718445032868</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.01266102623725594</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.01002316210915782</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.1065552772304499</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>-0.1360708653978901</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.001210425908114656</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0.01272257292574894</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>-0.1380314408029221</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>-0.04931454013247535</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.001842262246244504</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.02862995150473301</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.03557421716145035</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>-0.0002806677053405016</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0.02082942180484479</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3561552094561809</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.01461528058761554</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1694420763771597</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.458521323972297</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.1102789994057584</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.2018632597813164</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1465111201749011</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.07553104724581572</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.007876688718292052</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.03464976315906569</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.09665422287576729</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.02606062933830711</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.08488158716828027</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.03306874014875513</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.04040985925056052</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.6217537319705323</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.249084820411675</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.2332395141950415</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.135114935993165</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.04281132621501573</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.06832195490147791</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.1260295790523302</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.06696925129965003</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.01953724545125728</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.3411608812292869</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.07307565348040981</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.09965930652981776</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.1344627134980522</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.02891357264181775</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.05520665426580789</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.1578737967648144</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.1295763037828263</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.04113031461876673</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.1334574077807954</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.009649718205298915</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.09003843107199654</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.1238957146065747</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.150356751023435</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.04467446007604269</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.0661098626288933</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.01719623413709689</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.08201267498289817</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.1139802183926919</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.01200187027782812</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.03985380071440289</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.05218372615602367</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>-0.01467112117566057</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.03206792854761053</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.0003053247773973022</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.06739061810821176</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>-0.008891259718828991</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.1631816084359385</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.001389971623575849</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.06725347772217231</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.1320946920479579</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0.05678255439823746</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.1266320479029765</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>-0.04446245977870753</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.08519225740179022</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.08947966535098101</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.04855988178326866</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.09211269633916952</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1882110493962542</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.06045011990876518</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.05421460570442766</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2110355612503737</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.1039875227563408</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.06996815741817482</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.06693522986749528</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.05664364391215002</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.0005129352933645212</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.02132938520028196</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.08088347264416554</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.009018390043302096</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.01913657953203688</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.03062706281379629</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.004693817315653992</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.2266115782985005</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.145330729695395</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.09853189751102084</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.02383948056652564</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.01107981184061812</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-0.004555512201934471</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.03032304300893514</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.05734420124322059</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.00146724886016697</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.1393325263214533</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.04971113636392628</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-0.03280777421678921</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.05109707314923981</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.03454183876396445</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.0249105440611295</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.03508389259614986</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.06448405131386944</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.01860487659965929</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.05209998308849489</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.03055166470608029</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.04097352096899508</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0.0421109602686331</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0.04799596242865481</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.01876189037900398</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0.009947605153466864</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0.03213320907226954</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.002997059674717925</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0.009569568202845054</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0.01464041644138355</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0.0005874317185881181</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.03550930242807893</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.02871937809821762</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>-0.000281688692403851</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0.03241884057549319</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.02770606008508206</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.05811185893029152</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.05935953479975308</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.02291320481354426</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.02479693714673908</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.06738773654049734</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0.04374882171900592</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.04723932953933693</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>-0.01890200464484447</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.03405241870315608</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>-0.02645018188304403</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>-0.04973273716690825</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.04401042156084667</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.3062621012287385</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1697439887933007</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.0225764665038691</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.3939207168206099</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.2531493667990426</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.09192798131223728</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.05789105178514804</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.03918263396696085</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.04445156744560246</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.04485801167459334</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.05333421971266995</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.05307189229006939</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.05192491251099765</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0.04377870580929619</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.02117144196166106</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.2575395137183636</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-0.147913934313617</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.1613422457414024</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0.01447469927009988</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-0.05451169802822368</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.01775438806051417</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0.006056693819026982</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.09277562056780238</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.02356802591713684</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.2227348303611567</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>-0.1346086700475823</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0.01673392016931894</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0.08798674278981493</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.1092254433734384</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.009917785015196717</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0.07535502822328677</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0.1512510882441717</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0.06279368223697782</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-0.09501287022723083</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0.1253542683111722</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0.01396715145059126</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0.03142191938448079</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0.01431398198311158</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0.06074378955821807</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0.0542819856213192</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0.05413289384032118</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0.006878759574571309</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0.01413937685283034</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0.0045694481874441</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0.06821763240387074</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0.05776091201670293</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0.07960240122194492</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0.03733829365244858</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0.04331995973016383</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0.0698947308676152</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0.04105721911303054</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0.1066470505928781</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0.1262997108692964</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0.01145451723541879</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0.1058151841882729</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>-0.1328683143136258</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>-0.04048528250271507</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>-0.03453674521063502</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0.07805516102907843</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0.04958603112066189</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>-0.03266981396883647</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0.03408148225936678</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.2411690364911572</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.005911986604263595</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5540509205360705</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.3432819206269543</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.08923169712277691</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.6351761821921054</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.09498866176126582</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1051662558247142</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1149564887097962</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.01500105883367181</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.2366570115287204</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.07675873135285678</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.07704815412691571</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.09902014046926969</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.1527786750074216</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0.8473759477178021</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-0.04726322285607889</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.4100387753474432</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.2284381847852947</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.1728500302484692</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.02409376174185002</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-0.1834726476890839</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.1232398493663586</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-0.04917565605667395</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-0.4073900191066772</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.003747880418792714</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.3057745729754099</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.133164555492574</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-0.04212276935066037</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>-0.133590487712464</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0.2595376576066938</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0.05022343122817551</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>-0.1577381871665435</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0.1126652451398501</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>-0.03115033941937858</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>-0.1567143262575099</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0.03921984524070899</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.1046123052046541</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>-0.01773560369533675</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>-0.06967569056955145</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>0.004232527491140347</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>-0.139725175989181</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>0.1220445460937604</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>0.07832323143985638</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>-0.04836159207382045</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0.04707088431702191</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>-0.02326332848331636</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>0.01990768360923671</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0.03734326586328111</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>0.002975519151148031</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>-0.05912124889010575</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>0.1414988993799485</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>0.01943491402371648</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>-0.1415963025914871</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>-0.1608143449826339</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>0.009388256620079312</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>0.157809147952168</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>0.1270769400274785</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>-0.06533473368200933</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>0.09012469324595607</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>0.05456294578151856</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>-0.02955698747933388</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG18" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
